--- a/artfynd/A 47710-2024 artfynd.xlsx
+++ b/artfynd/A 47710-2024 artfynd.xlsx
@@ -798,43 +798,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120901005</v>
+        <v>120901004</v>
       </c>
       <c r="B3" t="n">
-        <v>94737</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587895</v>
+        <v>588045</v>
       </c>
       <c r="R3" t="n">
-        <v>6548821</v>
+        <v>6548791</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,46 +917,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120901004</v>
+        <v>120901005</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>94737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588045</v>
+        <v>587895</v>
       </c>
       <c r="R4" t="n">
-        <v>6548791</v>
+        <v>6548821</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47710-2024 artfynd.xlsx
+++ b/artfynd/A 47710-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120901002</v>
+        <v>120901004</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,11 +713,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587933</v>
+        <v>588045</v>
       </c>
       <c r="R2" t="n">
-        <v>6548813</v>
+        <v>6548791</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120901004</v>
+        <v>120901008</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>97038</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,34 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588045</v>
+        <v>587899</v>
       </c>
       <c r="R3" t="n">
-        <v>6548791</v>
+        <v>6548822</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,43 +910,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120901005</v>
+        <v>120901002</v>
       </c>
       <c r="B4" t="n">
-        <v>94737</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587895</v>
+        <v>587933</v>
       </c>
       <c r="R4" t="n">
-        <v>6548821</v>
+        <v>6548813</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120901000</v>
+        <v>120924944</v>
       </c>
       <c r="B5" t="n">
-        <v>79216</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,40 +1049,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långkärret 500m SO, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588024</v>
+        <v>588067</v>
       </c>
       <c r="R5" t="n">
-        <v>6548799</v>
+        <v>6548815</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,54 +1117,45 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med kolflarnlav</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120924944</v>
+        <v>120901000</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,48 +1168,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärret 500m SO, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588067</v>
+        <v>588024</v>
       </c>
       <c r="R6" t="n">
-        <v>6548815</v>
+        <v>6548799</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,35 +1228,44 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med kolflarnlav</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>120928449</v>
       </c>
       <c r="B7" t="n">
-        <v>97029</v>
+        <v>97039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120908308</v>
+        <v>120901001</v>
       </c>
       <c r="B8" t="n">
-        <v>105176</v>
+        <v>91102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,41 +1396,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långkärret 500m  SO, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587993</v>
+        <v>587908</v>
       </c>
       <c r="R8" t="n">
-        <v>6548777</v>
+        <v>6548818</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,45 +1464,49 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120901001</v>
+        <v>120908308</v>
       </c>
       <c r="B9" t="n">
-        <v>91092</v>
+        <v>105186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,48 +1519,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långkärret 500m  SO, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587908</v>
+        <v>587993</v>
       </c>
       <c r="R9" t="n">
-        <v>6548818</v>
+        <v>6548777</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,81 +1580,78 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120900999</v>
+        <v>120901005</v>
       </c>
       <c r="B10" t="n">
-        <v>78334</v>
+        <v>94747</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1658,10 +1659,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588024</v>
+        <v>587895</v>
       </c>
       <c r="R10" t="n">
-        <v>6548806</v>
+        <v>6548821</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1693,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,12 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe. Full träff på artefakta och Artsorakel mha bilder</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120901008</v>
+        <v>120900999</v>
       </c>
       <c r="B11" t="n">
-        <v>97028</v>
+        <v>78337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,31 +1743,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1779,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587899</v>
+        <v>588024</v>
       </c>
       <c r="R11" t="n">
-        <v>6548822</v>
+        <v>6548806</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1814,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1824,7 +1819,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe. Full träff på artefakta och Artsorakel mha bilder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,7 +1854,7 @@
         <v>120928074</v>
       </c>
       <c r="B12" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>121063402</v>
       </c>
       <c r="B13" t="n">
-        <v>97027</v>
+        <v>97037</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 47710-2024 artfynd.xlsx
+++ b/artfynd/A 47710-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120901004</v>
+        <v>120901000</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588045</v>
+        <v>588024</v>
       </c>
       <c r="R2" t="n">
-        <v>6548791</v>
+        <v>6548799</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med kolflarnlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120901008</v>
+        <v>120928074</v>
       </c>
       <c r="B3" t="n">
-        <v>97038</v>
+        <v>105186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,17 +835,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långkärret 500m SO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587899</v>
+        <v>588094</v>
       </c>
       <c r="R3" t="n">
-        <v>6548822</v>
+        <v>6548810</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,49 +872,45 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120901002</v>
+        <v>120908308</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>105186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,52 +919,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långkärret 500m  SO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587933</v>
+        <v>587993</v>
       </c>
       <c r="R4" t="n">
-        <v>6548813</v>
+        <v>6548777</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,49 +984,45 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120924944</v>
+        <v>120901008</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>97038</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,52 +1031,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärret 500m SO, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588067</v>
+        <v>587899</v>
       </c>
       <c r="R5" t="n">
-        <v>6548815</v>
+        <v>6548822</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,45 +1096,49 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120901000</v>
+        <v>120901002</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,25 +1151,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1195,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588024</v>
+        <v>587933</v>
       </c>
       <c r="R6" t="n">
-        <v>6548799</v>
+        <v>6548813</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med kolflarnlav</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120928449</v>
+        <v>120900999</v>
       </c>
       <c r="B7" t="n">
-        <v>97039</v>
+        <v>78337</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,41 +1270,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224364</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långkärret 500m SO, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588094</v>
+        <v>588024</v>
       </c>
       <c r="R7" t="n">
-        <v>6548810</v>
+        <v>6548806</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,35 +1334,44 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe. Full träff på artefakta och Artsorakel mha bilder</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1503,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120908308</v>
+        <v>120901004</v>
       </c>
       <c r="B9" t="n">
-        <v>105186</v>
+        <v>92008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,45 +1513,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långkärret 500m  SO, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587993</v>
+        <v>588045</v>
       </c>
       <c r="R9" t="n">
-        <v>6548777</v>
+        <v>6548791</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,35 +1581,39 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1731,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120900999</v>
+        <v>120924944</v>
       </c>
       <c r="B11" t="n">
-        <v>78337</v>
+        <v>92008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,40 +1752,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långkärret 500m SO, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588024</v>
+        <v>588067</v>
       </c>
       <c r="R11" t="n">
-        <v>6548806</v>
+        <v>6548815</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,54 +1820,45 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe. Full träff på artefakta och Artsorakel mha bilder</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120928074</v>
+        <v>120928449</v>
       </c>
       <c r="B12" t="n">
-        <v>105186</v>
+        <v>97039</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,23 +1871,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>224364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>

--- a/artfynd/A 47710-2024 artfynd.xlsx
+++ b/artfynd/A 47710-2024 artfynd.xlsx
@@ -1966,7 +1966,7 @@
         <v>121063402</v>
       </c>
       <c r="B13" t="n">
-        <v>97037</v>
+        <v>97050</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
